--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A685F691-1E4E-4538-ABD3-555504189A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FEEE013-2838-4139-AE07-0F5EB923CDAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="[$$-240A]\ #,##0.00;\-[$$-240A]\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="[$$-240A]\ #,##0.00;\-[$$-240A]\ #,##0.00"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -94,7 +94,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -117,6 +117,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="REQUERIMIENTO COMPRAS"/>
@@ -147,12 +148,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>204677.34834400003</v>
+            <v>168984.05085980528</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>302799.68968631624</v>
+            <v>289746.22206909629</v>
           </cell>
         </row>
       </sheetData>
@@ -197,6 +198,7 @@
       <sheetName val="INVENTARIO NACIONAL 07-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 10-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 11-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 12-08-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -210,10 +212,11 @@
       <sheetData sheetId="8">
         <row r="63">
           <cell r="D63">
-            <v>422625.38999999996</v>
+            <v>380946.38</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="9"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -771,15 +774,15 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>204677.34834400003</v>
+        <v>168984.05085980528</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>302799.68968631624</v>
+        <v>289746.22206909629</v>
       </c>
       <c r="C2" s="1">
         <f>'[2]INVENTARIO NACIONAL 11-08-26'!$D$63</f>
-        <v>422625.38999999996</v>
+        <v>380946.38</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FEEE013-2838-4139-AE07-0F5EB923CDAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A52C73-578C-4EAB-A15D-3BD7051A28C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -148,12 +148,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>168984.05085980528</v>
+            <v>165906.11128794134</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>289746.22206909629</v>
+            <v>290826.97207295347</v>
           </cell>
         </row>
       </sheetData>
@@ -209,14 +209,14 @@
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
-      <sheetData sheetId="8">
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9">
         <row r="63">
           <cell r="D63">
-            <v>380946.38</v>
+            <v>429676.42</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="9"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -774,15 +774,15 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>168984.05085980528</v>
+        <v>165906.11128794134</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>289746.22206909629</v>
+        <v>290826.97207295347</v>
       </c>
       <c r="C2" s="1">
-        <f>'[2]INVENTARIO NACIONAL 11-08-26'!$D$63</f>
-        <v>380946.38</v>
+        <f>'[2]INVENTARIO NACIONAL 12-08-26'!$D$63</f>
+        <v>429676.42</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A52C73-578C-4EAB-A15D-3BD7051A28C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E963A41-2D8E-4AA9-8154-5EAA7916BB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -148,12 +148,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>165906.11128794134</v>
+            <v>161744.66636413787</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>290826.97207295347</v>
+            <v>284258.38482340542</v>
           </cell>
         </row>
       </sheetData>
@@ -189,9 +189,6 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="VINCULO VTS BY SKU JULIO"/>
-      <sheetName val="VINCULO VTS BY SKU OPEN"/>
-      <sheetName val="DESV. VTS BY SKU"/>
       <sheetName val="INVENTARIO NACIONAL 04-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 05-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 06-08-26"/>
@@ -199,6 +196,11 @@
       <sheetName val="INVENTARIO NACIONAL 10-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 11-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 12-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 13-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 14-08-26"/>
+      <sheetName val="VINCULO VTS BY SKU JULIO"/>
+      <sheetName val="VINCULO VTS BY SKU OPEN"/>
+      <sheetName val="DESV. VTS BY SKU"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -209,14 +211,16 @@
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9">
-        <row r="63">
-          <cell r="D63">
-            <v>429676.42</v>
+      <sheetData sheetId="8">
+        <row r="66">
+          <cell r="D66">
+            <v>409347.87999999995</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -774,15 +778,15 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>165906.11128794134</v>
+        <v>161744.66636413787</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>290826.97207295347</v>
+        <v>284258.38482340542</v>
       </c>
       <c r="C2" s="1">
-        <f>'[2]INVENTARIO NACIONAL 12-08-26'!$D$63</f>
-        <v>429676.42</v>
+        <f>'[2]INVENTARIO NACIONAL 14-08-26'!$D$66</f>
+        <v>409347.87999999995</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E963A41-2D8E-4AA9-8154-5EAA7916BB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53F79C8-F77E-4A6A-B54F-C1BC179DFC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -148,12 +148,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>161744.66636413787</v>
+            <v>200219.36641545361</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>284258.38482340542</v>
+            <v>276684.66543270595</v>
           </cell>
         </row>
       </sheetData>
@@ -198,6 +198,7 @@
       <sheetName val="INVENTARIO NACIONAL 12-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 13-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 14-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -221,6 +222,7 @@
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -778,11 +780,11 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>161744.66636413787</v>
+        <v>200219.36641545361</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>284258.38482340542</v>
+        <v>276684.66543270595</v>
       </c>
       <c r="C2" s="1">
         <f>'[2]INVENTARIO NACIONAL 14-08-26'!$D$66</f>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53F79C8-F77E-4A6A-B54F-C1BC179DFC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEA2E79-8F3A-41F5-A10A-D0E628E82390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -199,6 +199,7 @@
       <sheetName val="INVENTARIO NACIONAL 13-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 14-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 18-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -212,17 +213,18 @@
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
-      <sheetData sheetId="8">
-        <row r="66">
-          <cell r="D66">
-            <v>409347.87999999995</v>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10">
+        <row r="69">
+          <cell r="D69">
+            <v>441097.37999999995</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -787,8 +789,8 @@
         <v>276684.66543270595</v>
       </c>
       <c r="C2" s="1">
-        <f>'[2]INVENTARIO NACIONAL 14-08-26'!$D$66</f>
-        <v>409347.87999999995</v>
+        <f>'[2]INVENTARIO NACIONAL 18-08-26'!$D$69</f>
+        <v>441097.37999999995</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEA2E79-8F3A-41F5-A10A-D0E628E82390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B939FC5C-41D9-49B7-87A5-26A311B1747C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -200,6 +200,7 @@
       <sheetName val="INVENTARIO NACIONAL 14-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 18-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 19-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -215,16 +216,17 @@
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
-      <sheetData sheetId="10">
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11">
         <row r="69">
           <cell r="D69">
-            <v>441097.37999999995</v>
+            <v>421707.75999999995</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -789,8 +791,8 @@
         <v>276684.66543270595</v>
       </c>
       <c r="C2" s="1">
-        <f>'[2]INVENTARIO NACIONAL 18-08-26'!$D$69</f>
-        <v>441097.37999999995</v>
+        <f>'[2]INVENTARIO NACIONAL 19-08-26'!$D$69</f>
+        <v>421707.75999999995</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B939FC5C-41D9-49B7-87A5-26A311B1747C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB88D2A5-6088-4D04-8EA5-1DF89948E486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -148,12 +148,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>200219.36641545361</v>
+            <v>160068.50721729058</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>276684.66543270595</v>
+            <v>269664.14633368974</v>
           </cell>
         </row>
       </sheetData>
@@ -201,6 +201,8 @@
       <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 18-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 19-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 19-08-26-2"/>
+      <sheetName val="INVENTARIO NACIONAL 20-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -217,16 +219,18 @@
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
-      <sheetData sheetId="11">
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13">
         <row r="69">
           <cell r="D69">
-            <v>421707.75999999995</v>
+            <v>423500.63999999984</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -784,15 +788,15 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>200219.36641545361</v>
+        <v>160068.50721729058</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>276684.66543270595</v>
+        <v>269664.14633368974</v>
       </c>
       <c r="C2" s="1">
-        <f>'[2]INVENTARIO NACIONAL 19-08-26'!$D$69</f>
-        <v>421707.75999999995</v>
+        <f>'[2]INVENTARIO NACIONAL 20-08-26'!$D$69</f>
+        <v>423500.63999999984</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB88D2A5-6088-4D04-8EA5-1DF89948E486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{608FC23D-BF8D-401D-BE33-6521DCCFEB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -26,7 +26,7 @@
     <externalReference r:id="rId9"/>
     <externalReference r:id="rId10"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -148,12 +148,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>160068.50721729058</v>
+            <v>242358.19263423263</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>269664.14633368974</v>
+            <v>320205.97566983633</v>
           </cell>
         </row>
       </sheetData>
@@ -203,6 +203,9 @@
       <sheetName val="INVENTARIO NACIONAL 19-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 19-08-26-2"/>
       <sheetName val="INVENTARIO NACIONAL 20-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 20-08-26-2"/>
+      <sheetName val="INVENTARIO NACIONAL 21-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 24-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -231,6 +234,9 @@
       <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
       <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -788,11 +794,11 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>160068.50721729058</v>
+        <v>242358.19263423263</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>269664.14633368974</v>
+        <v>320205.97566983633</v>
       </c>
       <c r="C2" s="1">
         <f>'[2]INVENTARIO NACIONAL 20-08-26'!$D$69</f>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{608FC23D-BF8D-401D-BE33-6521DCCFEB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1647282E-3F2D-4DAB-ADF0-514A91B76D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -148,12 +148,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>242358.19263423263</v>
+            <v>273914.7186931668</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>320205.97566983633</v>
+            <v>326625.68646658427</v>
           </cell>
         </row>
       </sheetData>
@@ -206,6 +206,7 @@
       <sheetName val="INVENTARIO NACIONAL 20-08-26-2"/>
       <sheetName val="INVENTARIO NACIONAL 21-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 24-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 25-08-26"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -237,6 +238,7 @@
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -794,11 +796,11 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>242358.19263423263</v>
+        <v>273914.7186931668</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>320205.97566983633</v>
+        <v>326625.68646658427</v>
       </c>
       <c r="C2" s="1">
         <f>'[2]INVENTARIO NACIONAL 20-08-26'!$D$69</f>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1647282E-3F2D-4DAB-ADF0-514A91B76D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834E9EDA-43B9-47BA-9349-5324C1DF29C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -207,6 +207,9 @@
       <sheetName val="INVENTARIO NACIONAL 21-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 24-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 25-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 25-08-26-2"/>
+      <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
+      <sheetName val="Hoja1"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -239,6 +242,9 @@
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834E9EDA-43B9-47BA-9349-5324C1DF29C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE02CCD-372D-4035-B5BB-5CFA7F4169BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -26,7 +26,7 @@
     <externalReference r:id="rId9"/>
     <externalReference r:id="rId10"/>
   </externalReferences>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -209,6 +209,7 @@
       <sheetName val="INVENTARIO NACIONAL 25-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 25-08-26-2"/>
       <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 28-08-26"/>
       <sheetName val="Hoja1"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -245,6 +246,7 @@
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
       <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE02CCD-372D-4035-B5BB-5CFA7F4169BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793376F0-A571-4290-9E07-2960A484EEDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -210,7 +210,8 @@
       <sheetName val="INVENTARIO NACIONAL 25-08-26-2"/>
       <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 28-08-26"/>
-      <sheetName val="Hoja1"/>
+      <sheetName val="INVENTARIO NACIONAL 31-08-26"/>
+      <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
@@ -229,24 +230,25 @@
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
-      <sheetData sheetId="13">
-        <row r="69">
-          <cell r="D69">
-            <v>423500.63999999984</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
+      <sheetData sheetId="20">
+        <row r="68">
+          <cell r="D68">
+            <v>373593.25000000017</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
       <sheetData sheetId="23"/>
       <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -811,8 +813,8 @@
         <v>326625.68646658427</v>
       </c>
       <c r="C2" s="1">
-        <f>'[2]INVENTARIO NACIONAL 20-08-26'!$D$69</f>
-        <v>423500.63999999984</v>
+        <f>'[2]INVENTARIO NACIONAL 28-08-26'!$D$68</f>
+        <v>373593.25000000017</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793376F0-A571-4290-9E07-2960A484EEDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4418595-2247-4114-BCDB-EBEE3B458DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -211,6 +211,7 @@
       <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 28-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 31-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL CIERRE"/>
       <sheetName val="CCC"/>
       <sheetName val="VINCULO VTS BY SKU JULIO"/>
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
@@ -237,18 +238,19 @@
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
-      <sheetData sheetId="20">
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21">
         <row r="68">
           <cell r="D68">
-            <v>373593.25000000017</v>
+            <v>396069.85000000015</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="21"/>
       <sheetData sheetId="22"/>
       <sheetData sheetId="23"/>
       <sheetData sheetId="24"/>
       <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -813,8 +815,8 @@
         <v>326625.68646658427</v>
       </c>
       <c r="C2" s="1">
-        <f>'[2]INVENTARIO NACIONAL 28-08-26'!$D$68</f>
-        <v>373593.25000000017</v>
+        <f>'[2]INVENTARIO NACIONAL 31-08-26'!$D$68</f>
+        <v>396069.85000000015</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4418595-2247-4114-BCDB-EBEE3B458DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DA0801-DDDD-4BCA-BF9C-DA42AD5E1D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -24,7 +24,6 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId9"/>
-    <externalReference r:id="rId10"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -177,80 +176,6 @@
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="INVENTARIO NACIONAL 04-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 05-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 06-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 07-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 10-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 11-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 12-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 13-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 14-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 17-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 18-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 19-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 19-08-26-2"/>
-      <sheetName val="INVENTARIO NACIONAL 20-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 20-08-26-2"/>
-      <sheetName val="INVENTARIO NACIONAL 21-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 24-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 25-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 25-08-26-2"/>
-      <sheetName val="INVENTARIO NACIONAL 27-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 28-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL 31-08-26"/>
-      <sheetName val="INVENTARIO NACIONAL CIERRE"/>
-      <sheetName val="CCC"/>
-      <sheetName val="VINCULO VTS BY SKU JULIO"/>
-      <sheetName val="VINCULO VTS BY SKU OPEN"/>
-      <sheetName val="DESV. VTS BY SKU"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21">
-        <row r="68">
-          <cell r="D68">
-            <v>396069.85000000015</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -815,8 +740,7 @@
         <v>326625.68646658427</v>
       </c>
       <c r="C2" s="1">
-        <f>'[2]INVENTARIO NACIONAL 31-08-26'!$D$68</f>
-        <v>396069.85000000015</v>
+        <v>371878.13999999996</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DA0801-DDDD-4BCA-BF9C-DA42AD5E1D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A00A1C-8426-4B2C-BC65-AA7615EA0027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
   <sheets>
     <sheet name="ENERO 2026" sheetId="2" r:id="rId1"/>
@@ -21,9 +21,11 @@
     <sheet name="JUNIO 2026" sheetId="10" r:id="rId6"/>
     <sheet name="JULIO 2026" sheetId="8" r:id="rId7"/>
     <sheet name="AGOSTO 2026" sheetId="9" r:id="rId8"/>
+    <sheet name="SEPTIEMBRE 2026" sheetId="11" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="3">
   <si>
     <t>VALOR $ MATERIA PRIMA</t>
   </si>
@@ -122,22 +124,22 @@
       <sheetName val="REQUERIMIENTO COMPRAS"/>
       <sheetName val="DASHBOARD FINANCIERO"/>
       <sheetName val="VINCULO VTS BY SKU"/>
+      <sheetName val="FILL RATE"/>
       <sheetName val="MPS"/>
-      <sheetName val="FILL RATE"/>
       <sheetName val="BOM (Recetas)"/>
       <sheetName val="Explosión de materiales"/>
-      <sheetName val="FOTORequerimienMateriaPrima08"/>
+      <sheetName val="FOTORequerimienMateriaPrima09"/>
       <sheetName val="Requerimiento Materia Prima"/>
       <sheetName val="VINCULO MP"/>
       <sheetName val="VALOR $ CONSUMO MP"/>
-      <sheetName val="FOTORequerimienMaterialConten08"/>
+      <sheetName val="FOTORequerimienMaterialConten09"/>
       <sheetName val="Requerimien Material Contenedor"/>
       <sheetName val="VINCULO MC"/>
       <sheetName val="VALOR $ CONSUMO MC"/>
-      <sheetName val="FOTORequerimientoMaterialEmpa08"/>
+      <sheetName val="FOTORequerimientoMaterialEmpa09"/>
       <sheetName val="Requerimiento Material Empaque"/>
+      <sheetName val="VINCULO ME"/>
       <sheetName val="VALOR $ CONSUMO ME"/>
-      <sheetName val="VINCULO ME"/>
       <sheetName val="Plan Producción Semanal"/>
       <sheetName val="Plan Maduraciòn Semanal"/>
       <sheetName val="Panel Producción Diario"/>
@@ -147,12 +149,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>273914.7186931668</v>
+            <v>186408.39212143651</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>326625.68646658427</v>
+            <v>310222.90694886539</v>
           </cell>
         </row>
       </sheetData>
@@ -176,6 +178,28 @@
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Hoja1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="67">
+          <cell r="D67">
+            <v>415893.59999999992</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -732,15 +756,52 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
+        <v>186408.39212143651</v>
+      </c>
+      <c r="B2" s="1">
+        <v>310223</v>
+      </c>
+      <c r="C2" s="1">
+        <v>371878.13999999996</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD64BA53-62BA-4AC1-8141-AF32DE6DBCCD}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>273914.7186931668</v>
+        <v>186408.39212143651</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>326625.68646658427</v>
+        <v>310222.90694886539</v>
       </c>
       <c r="C2" s="1">
-        <v>371878.13999999996</v>
+        <f>[2]Hoja1!$D$67</f>
+        <v>415893.59999999992</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A00A1C-8426-4B2C-BC65-AA7615EA0027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBED8469-CF6B-4CDF-824C-13CEF623DCB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -756,10 +756,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>186408.39212143651</v>
+        <v>154039.39212143701</v>
       </c>
       <c r="B2" s="1">
-        <v>310223</v>
+        <v>292864</v>
       </c>
       <c r="C2" s="1">
         <v>371878.13999999996</v>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBED8469-CF6B-4CDF-824C-13CEF623DCB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13EA6D02-7AAB-4F19-B0FE-685E76BB3640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -149,12 +149,12 @@
       <sheetData sheetId="1">
         <row r="9">
           <cell r="B9">
-            <v>186408.39212143651</v>
+            <v>177521.71864408237</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10">
-            <v>310222.90694886539</v>
+            <v>274869.81610848685</v>
           </cell>
         </row>
       </sheetData>
@@ -196,7 +196,7 @@
       <sheetData sheetId="0">
         <row r="67">
           <cell r="D67">
-            <v>415893.59999999992</v>
+            <v>406406</v>
           </cell>
         </row>
       </sheetData>
@@ -793,15 +793,15 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$9</f>
-        <v>186408.39212143651</v>
+        <v>177521.71864408237</v>
       </c>
       <c r="B2" s="1">
         <f>'[1]DASHBOARD FINANCIERO'!$B$10</f>
-        <v>310222.90694886539</v>
+        <v>274869.81610848685</v>
       </c>
       <c r="C2" s="1">
         <f>[2]Hoja1!$D$67</f>
-        <v>415893.59999999992</v>
+        <v>406406</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico Cierre Inventario Valorizado.xlsx
+++ b/data/Historico Cierre Inventario Valorizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13EA6D02-7AAB-4F19-B0FE-685E76BB3640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC2D173-D66A-4EE8-A295-F300012C2FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{287844AE-1C75-4DEF-B5F9-A501B02DAC1F}"/>
   </bookViews>
@@ -196,7 +196,7 @@
       <sheetData sheetId="0">
         <row r="67">
           <cell r="D67">
-            <v>406406</v>
+            <v>416647.29000000004</v>
           </cell>
         </row>
       </sheetData>
@@ -801,7 +801,7 @@
       </c>
       <c r="C2" s="1">
         <f>[2]Hoja1!$D$67</f>
-        <v>406406</v>
+        <v>416647.29000000004</v>
       </c>
     </row>
   </sheetData>
